--- a/data/features_realtime.xlsx
+++ b/data/features_realtime.xlsx
@@ -42790,10 +42790,10 @@
         <v>26.6</v>
       </c>
       <c r="L356" t="n">
-        <v>2064.861312985157</v>
+        <v>2162.428673698428</v>
       </c>
       <c r="M356" t="n">
-        <v>2234.410562501981</v>
+        <v>2283.889578967151</v>
       </c>
       <c r="N356" t="n">
         <v>65.096</v>
@@ -42805,13 +42805,13 @@
         <v>0</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.9899039645640855</v>
+        <v>0.9452401482001956</v>
       </c>
       <c r="R356" t="n">
-        <v>-20.84691298515736</v>
+        <v>-118.4142736984281</v>
       </c>
       <c r="S356" t="n">
-        <v>0.08990396456408545</v>
+        <v>0.04524014820019562</v>
       </c>
       <c r="T356" t="n">
         <v>0</v>
@@ -42826,7 +42826,7 @@
         <v>0.2275213714227406</v>
       </c>
       <c r="X356" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y356" t="n">
         <v>3</v>
@@ -42909,10 +42909,10 @@
         <v>26.6</v>
       </c>
       <c r="L357" t="n">
-        <v>2139.375687434022</v>
+        <v>2114.352755772137</v>
       </c>
       <c r="M357" t="n">
-        <v>2232.284147825354</v>
+        <v>2221.441629972245</v>
       </c>
       <c r="N357" t="n">
         <v>65.12299999999999</v>
@@ -42924,13 +42924,13 @@
         <v>0</v>
       </c>
       <c r="Q357" t="n">
-        <v>0.9570395382284563</v>
+        <v>0.9683659050787485</v>
       </c>
       <c r="R357" t="n">
-        <v>-91.90856743402219</v>
+        <v>-66.88563577213699</v>
       </c>
       <c r="S357" t="n">
-        <v>0.05703953822845631</v>
+        <v>0.06836590507874851</v>
       </c>
       <c r="T357" t="n">
         <v>0</v>
@@ -43028,10 +43028,10 @@
         <v>26.6</v>
       </c>
       <c r="L358" t="n">
-        <v>2139.375687434022</v>
+        <v>2114.352755772137</v>
       </c>
       <c r="M358" t="n">
-        <v>2232.284147825354</v>
+        <v>2221.441629972245</v>
       </c>
       <c r="N358" t="n">
         <v>65.378</v>
@@ -43043,10 +43043,10 @@
         <v>0</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.9570395382284563</v>
+        <v>0.9683659050787485</v>
       </c>
       <c r="R358" t="n">
-        <v>-91.90856743402219</v>
+        <v>-66.88563577213699</v>
       </c>
       <c r="S358" t="n">
         <v>0</v>
@@ -43147,10 +43147,10 @@
         <v>26.6</v>
       </c>
       <c r="L359" t="n">
-        <v>2120.854782621622</v>
+        <v>2076.105066030535</v>
       </c>
       <c r="M359" t="n">
-        <v>2430.281555155684</v>
+        <v>2199.670220701716</v>
       </c>
       <c r="N359" t="n">
         <v>64.702</v>
@@ -43162,13 +43162,13 @@
         <v>0</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.9591561367933434</v>
+        <v>0.9798304109379311</v>
       </c>
       <c r="R359" t="n">
-        <v>-86.62390262162171</v>
+        <v>-41.87418603053538</v>
       </c>
       <c r="S359" t="n">
-        <v>0.05915613679334342</v>
+        <v>0.07983041093793108</v>
       </c>
       <c r="T359" t="n">
         <v>0.9914454612489136</v>
@@ -43266,10 +43266,10 @@
         <v>26.6</v>
       </c>
       <c r="L360" t="n">
-        <v>2376.134610994433</v>
+        <v>2293.575106701664</v>
       </c>
       <c r="M360" t="n">
-        <v>2282.755127792026</v>
+        <v>2212.005445750439</v>
       </c>
       <c r="N360" t="n">
         <v>67.26499999999999</v>
@@ -43281,13 +43281,13 @@
         <v>0</v>
       </c>
       <c r="Q360" t="n">
-        <v>0.9264294598451327</v>
+        <v>0.956060756569059</v>
       </c>
       <c r="R360" t="n">
-        <v>-167.9435277920261</v>
+        <v>-97.19384575043978</v>
       </c>
       <c r="S360" t="n">
-        <v>0.02642945984513267</v>
+        <v>0.05606075656905896</v>
       </c>
       <c r="T360" t="n">
         <v>1.019254799485697</v>
@@ -43302,7 +43302,7 @@
         <v>0.2253165487596696</v>
       </c>
       <c r="X360" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y360" t="n">
         <v>2</v>
@@ -43385,10 +43385,10 @@
         <v>26.6</v>
       </c>
       <c r="L361" t="n">
-        <v>2208.51200606845</v>
+        <v>2321.441445956119</v>
       </c>
       <c r="M361" t="n">
-        <v>2351.480088087601</v>
+        <v>2266.269352705333</v>
       </c>
       <c r="N361" t="n">
         <v>68.613</v>
@@ -43400,13 +43400,13 @@
         <v>44.41118000000006</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.9767629580783741</v>
+        <v>0.9518695195802405</v>
       </c>
       <c r="R361" t="n">
-        <v>-51.31928606844986</v>
+        <v>-109.0766327053334</v>
       </c>
       <c r="S361" t="n">
-        <v>0.07676295807837408</v>
+        <v>0.05186951958024044</v>
       </c>
       <c r="T361" t="n">
         <v>1.029142873202775</v>
@@ -43504,10 +43504,10 @@
         <v>26.6</v>
       </c>
       <c r="L362" t="n">
-        <v>2132.032886783272</v>
+        <v>2172.547733282463</v>
       </c>
       <c r="M362" t="n">
-        <v>2501.603505669199</v>
+        <v>2282.863921419112</v>
       </c>
       <c r="N362" t="n">
         <v>68.508</v>
@@ -43519,13 +43519,13 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q362" t="n">
-        <v>1.010252484073403</v>
+        <v>0.9914127487292227</v>
       </c>
       <c r="R362" t="n">
-        <v>21.85863321672787</v>
+        <v>-18.65621328246289</v>
       </c>
       <c r="S362" t="n">
-        <v>0.1102524840734033</v>
+        <v>0.09141274872922267</v>
       </c>
       <c r="T362" t="n">
         <v>1.015267388620419</v>
@@ -43540,7 +43540,7 @@
         <v>0.2245949852590114</v>
       </c>
       <c r="X362" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y362" t="n">
         <v>4</v>
@@ -43623,10 +43623,10 @@
         <v>26.6</v>
       </c>
       <c r="L363" t="n">
-        <v>2132.032886783272</v>
+        <v>2172.547733282463</v>
       </c>
       <c r="M363" t="n">
-        <v>2501.603505669199</v>
+        <v>2282.863921419112</v>
       </c>
       <c r="N363" t="n">
         <v>68.02199999999999</v>
@@ -43638,10 +43638,10 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q363" t="n">
-        <v>1.010252484073403</v>
+        <v>0.9914127487292227</v>
       </c>
       <c r="R363" t="n">
-        <v>21.85863321672787</v>
+        <v>-18.65621328246289</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -43742,10 +43742,10 @@
         <v>26.6</v>
       </c>
       <c r="L364" t="n">
-        <v>2132.032886783272</v>
+        <v>2172.547733282463</v>
       </c>
       <c r="M364" t="n">
-        <v>2501.603505669199</v>
+        <v>2282.863921419112</v>
       </c>
       <c r="N364" t="n">
         <v>68.02199999999999</v>
@@ -43757,10 +43757,10 @@
         <v>100.0611466666664</v>
       </c>
       <c r="Q364" t="n">
-        <v>1.010252484073403</v>
+        <v>0.9914127487292227</v>
       </c>
       <c r="R364" t="n">
-        <v>21.85863321672787</v>
+        <v>-18.65621328246289</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -43861,10 +43861,10 @@
         <v>26.6</v>
       </c>
       <c r="L365" t="n">
-        <v>2132.032886783272</v>
+        <v>2172.547733282463</v>
       </c>
       <c r="M365" t="n">
-        <v>2501.603505669199</v>
+        <v>2282.863921419112</v>
       </c>
       <c r="N365" t="n">
         <v>68.02199999999999</v>
@@ -43876,10 +43876,10 @@
         <v>95.41112000000021</v>
       </c>
       <c r="Q365" t="n">
-        <v>1.010252484073403</v>
+        <v>0.9914127487292227</v>
       </c>
       <c r="R365" t="n">
-        <v>21.85863321672787</v>
+        <v>-18.65621328246289</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -43980,10 +43980,10 @@
         <v>26.6</v>
       </c>
       <c r="L366" t="n">
-        <v>2132.032886783272</v>
+        <v>2172.547733282463</v>
       </c>
       <c r="M366" t="n">
-        <v>2501.603505669199</v>
+        <v>2282.863921419112</v>
       </c>
       <c r="N366" t="n">
         <v>68.02199999999999</v>
@@ -43995,10 +43995,10 @@
         <v>65.46594000000005</v>
       </c>
       <c r="Q366" t="n">
-        <v>1.010252484073403</v>
+        <v>0.9914127487292227</v>
       </c>
       <c r="R366" t="n">
-        <v>21.85863321672787</v>
+        <v>-18.65621328246289</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>

--- a/data/features_realtime.xlsx
+++ b/data/features_realtime.xlsx
@@ -42790,10 +42790,10 @@
         <v>26.6</v>
       </c>
       <c r="L356" t="n">
-        <v>2162.428673698428</v>
+        <v>1879.04909542779</v>
       </c>
       <c r="M356" t="n">
-        <v>2283.889578967151</v>
+        <v>2281.638333784345</v>
       </c>
       <c r="N356" t="n">
         <v>65.096</v>
@@ -42805,13 +42805,13 @@
         <v>0</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.9452401482001956</v>
+        <v>1.087791907605036</v>
       </c>
       <c r="R356" t="n">
-        <v>-118.4142736984281</v>
+        <v>164.9653045722098</v>
       </c>
       <c r="S356" t="n">
-        <v>0.04524014820019562</v>
+        <v>0.1877919076050355</v>
       </c>
       <c r="T356" t="n">
         <v>0</v>
@@ -42826,7 +42826,7 @@
         <v>0.2275213714227406</v>
       </c>
       <c r="X356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y356" t="n">
         <v>3</v>
@@ -42909,10 +42909,10 @@
         <v>26.6</v>
       </c>
       <c r="L357" t="n">
-        <v>2114.352755772137</v>
+        <v>1897.144765468527</v>
       </c>
       <c r="M357" t="n">
-        <v>2221.441629972245</v>
+        <v>2194.770566540544</v>
       </c>
       <c r="N357" t="n">
         <v>65.12299999999999</v>
@@ -42924,13 +42924,13 @@
         <v>0</v>
       </c>
       <c r="Q357" t="n">
-        <v>0.9683659050787485</v>
+        <v>1.079236101148701</v>
       </c>
       <c r="R357" t="n">
-        <v>-66.88563577213699</v>
+        <v>150.3223545314725</v>
       </c>
       <c r="S357" t="n">
-        <v>0.06836590507874851</v>
+        <v>0.1792361011487013</v>
       </c>
       <c r="T357" t="n">
         <v>0</v>
@@ -42945,7 +42945,7 @@
         <v>0.2275890184142461</v>
       </c>
       <c r="X357" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y357" t="n">
         <v>4</v>
@@ -43028,10 +43028,10 @@
         <v>26.6</v>
       </c>
       <c r="L358" t="n">
-        <v>2114.352755772137</v>
+        <v>1897.144765468527</v>
       </c>
       <c r="M358" t="n">
-        <v>2221.441629972245</v>
+        <v>2194.770566540544</v>
       </c>
       <c r="N358" t="n">
         <v>65.378</v>
@@ -43043,10 +43043,10 @@
         <v>0</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.9683659050787485</v>
+        <v>1.079236101148701</v>
       </c>
       <c r="R358" t="n">
-        <v>-66.88563577213699</v>
+        <v>150.3223545314725</v>
       </c>
       <c r="S358" t="n">
         <v>0</v>
@@ -43147,10 +43147,10 @@
         <v>26.6</v>
       </c>
       <c r="L359" t="n">
-        <v>2076.105066030535</v>
+        <v>2059.913076100859</v>
       </c>
       <c r="M359" t="n">
-        <v>2199.670220701716</v>
+        <v>2338.48951730038</v>
       </c>
       <c r="N359" t="n">
         <v>64.702</v>
@@ -43162,13 +43162,13 @@
         <v>0</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.9798304109379311</v>
+        <v>0.9875323884294868</v>
       </c>
       <c r="R359" t="n">
-        <v>-41.87418603053538</v>
+        <v>-25.68219610085907</v>
       </c>
       <c r="S359" t="n">
-        <v>0.07983041093793108</v>
+        <v>0.08753238842948674</v>
       </c>
       <c r="T359" t="n">
         <v>0.9914454612489136</v>
@@ -43266,10 +43266,10 @@
         <v>26.6</v>
       </c>
       <c r="L360" t="n">
-        <v>2293.575106701664</v>
+        <v>2047.950198703286</v>
       </c>
       <c r="M360" t="n">
-        <v>2212.005445750439</v>
+        <v>2221.583333460699</v>
       </c>
       <c r="N360" t="n">
         <v>67.26499999999999</v>
@@ -43281,13 +43281,13 @@
         <v>0</v>
       </c>
       <c r="Q360" t="n">
-        <v>0.956060756569059</v>
+        <v>1.032647962503198</v>
       </c>
       <c r="R360" t="n">
-        <v>-97.19384575043978</v>
+        <v>66.86140129671389</v>
       </c>
       <c r="S360" t="n">
-        <v>0.05606075656905896</v>
+        <v>0.1326479625031977</v>
       </c>
       <c r="T360" t="n">
         <v>1.019254799485697</v>
@@ -43302,7 +43302,7 @@
         <v>0.2253165487596696</v>
       </c>
       <c r="X360" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y360" t="n">
         <v>2</v>
@@ -43385,10 +43385,10 @@
         <v>26.6</v>
       </c>
       <c r="L361" t="n">
-        <v>2321.441445956119</v>
+        <v>2263.730666801088</v>
       </c>
       <c r="M361" t="n">
-        <v>2266.269352705333</v>
+        <v>2629.244018708134</v>
       </c>
       <c r="N361" t="n">
         <v>68.613</v>
@@ -43400,13 +43400,13 @@
         <v>44.41118000000006</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.9518695195802405</v>
+        <v>0.9529370042273664</v>
       </c>
       <c r="R361" t="n">
-        <v>-109.0766327053334</v>
+        <v>-106.5379468010879</v>
       </c>
       <c r="S361" t="n">
-        <v>0.05186951958024044</v>
+        <v>0.05293700422736636</v>
       </c>
       <c r="T361" t="n">
         <v>1.029142873202775</v>
@@ -43504,10 +43504,10 @@
         <v>26.6</v>
       </c>
       <c r="L362" t="n">
-        <v>2172.547733282463</v>
+        <v>2433.618373589949</v>
       </c>
       <c r="M362" t="n">
-        <v>2282.863921419112</v>
+        <v>2266.389181079187</v>
       </c>
       <c r="N362" t="n">
         <v>68.508</v>
@@ -43519,13 +43519,13 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q362" t="n">
-        <v>0.9914127487292227</v>
+        <v>0.9503626023194438</v>
       </c>
       <c r="R362" t="n">
-        <v>-18.65621328246289</v>
+        <v>-112.4976610791873</v>
       </c>
       <c r="S362" t="n">
-        <v>0.09141274872922267</v>
+        <v>0.05036260231944378</v>
       </c>
       <c r="T362" t="n">
         <v>1.015267388620419</v>
@@ -43623,10 +43623,10 @@
         <v>26.6</v>
       </c>
       <c r="L363" t="n">
-        <v>2172.547733282463</v>
+        <v>2433.618373589949</v>
       </c>
       <c r="M363" t="n">
-        <v>2282.863921419112</v>
+        <v>2266.389181079187</v>
       </c>
       <c r="N363" t="n">
         <v>68.02199999999999</v>
@@ -43638,10 +43638,10 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q363" t="n">
-        <v>0.9914127487292227</v>
+        <v>0.9503626023194438</v>
       </c>
       <c r="R363" t="n">
-        <v>-18.65621328246289</v>
+        <v>-112.4976610791873</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -43742,10 +43742,10 @@
         <v>26.6</v>
       </c>
       <c r="L364" t="n">
-        <v>2172.547733282463</v>
+        <v>2433.618373589949</v>
       </c>
       <c r="M364" t="n">
-        <v>2282.863921419112</v>
+        <v>2266.389181079187</v>
       </c>
       <c r="N364" t="n">
         <v>68.02199999999999</v>
@@ -43757,10 +43757,10 @@
         <v>100.0611466666664</v>
       </c>
       <c r="Q364" t="n">
-        <v>0.9914127487292227</v>
+        <v>0.9503626023194438</v>
       </c>
       <c r="R364" t="n">
-        <v>-18.65621328246289</v>
+        <v>-112.4976610791873</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -43861,10 +43861,10 @@
         <v>26.6</v>
       </c>
       <c r="L365" t="n">
-        <v>2172.547733282463</v>
+        <v>2433.618373589949</v>
       </c>
       <c r="M365" t="n">
-        <v>2282.863921419112</v>
+        <v>2266.389181079187</v>
       </c>
       <c r="N365" t="n">
         <v>68.02199999999999</v>
@@ -43876,10 +43876,10 @@
         <v>95.41112000000021</v>
       </c>
       <c r="Q365" t="n">
-        <v>0.9914127487292227</v>
+        <v>0.9503626023194438</v>
       </c>
       <c r="R365" t="n">
-        <v>-18.65621328246289</v>
+        <v>-112.4976610791873</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -43980,10 +43980,10 @@
         <v>26.6</v>
       </c>
       <c r="L366" t="n">
-        <v>2172.547733282463</v>
+        <v>2433.618373589949</v>
       </c>
       <c r="M366" t="n">
-        <v>2282.863921419112</v>
+        <v>2266.389181079187</v>
       </c>
       <c r="N366" t="n">
         <v>68.02199999999999</v>
@@ -43995,10 +43995,10 @@
         <v>65.46594000000005</v>
       </c>
       <c r="Q366" t="n">
-        <v>0.9914127487292227</v>
+        <v>0.9503626023194438</v>
       </c>
       <c r="R366" t="n">
-        <v>-18.65621328246289</v>
+        <v>-112.4976610791873</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>

--- a/data/features_realtime.xlsx
+++ b/data/features_realtime.xlsx
@@ -42790,10 +42790,10 @@
         <v>26.6</v>
       </c>
       <c r="L356" t="n">
-        <v>1879.04909542779</v>
+        <v>2306.521189409711</v>
       </c>
       <c r="M356" t="n">
-        <v>2281.638333784345</v>
+        <v>2206.743157840859</v>
       </c>
       <c r="N356" t="n">
         <v>65.096</v>
@@ -42805,13 +42805,13 @@
         <v>0</v>
       </c>
       <c r="Q356" t="n">
-        <v>1.087791907605036</v>
+        <v>0.9262584060752209</v>
       </c>
       <c r="R356" t="n">
-        <v>164.9653045722098</v>
+        <v>-162.7287578408591</v>
       </c>
       <c r="S356" t="n">
-        <v>0.1877919076050355</v>
+        <v>0.0262584060752209</v>
       </c>
       <c r="T356" t="n">
         <v>0</v>
@@ -42826,7 +42826,7 @@
         <v>0.2275213714227406</v>
       </c>
       <c r="X356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y356" t="n">
         <v>3</v>
@@ -42909,10 +42909,10 @@
         <v>26.6</v>
       </c>
       <c r="L357" t="n">
-        <v>1897.144765468527</v>
+        <v>2304.696074558392</v>
       </c>
       <c r="M357" t="n">
-        <v>2194.770566540544</v>
+        <v>2148.852877740213</v>
       </c>
       <c r="N357" t="n">
         <v>65.12299999999999</v>
@@ -42924,13 +42924,13 @@
         <v>0</v>
       </c>
       <c r="Q357" t="n">
-        <v>1.079236101148701</v>
+        <v>0.9528186602296449</v>
       </c>
       <c r="R357" t="n">
-        <v>150.3223545314725</v>
+        <v>-101.3857577402136</v>
       </c>
       <c r="S357" t="n">
-        <v>0.1792361011487013</v>
+        <v>0.05281866022964488</v>
       </c>
       <c r="T357" t="n">
         <v>0</v>
@@ -42945,7 +42945,7 @@
         <v>0.2275890184142461</v>
       </c>
       <c r="X357" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y357" t="n">
         <v>4</v>
@@ -43028,10 +43028,10 @@
         <v>26.6</v>
       </c>
       <c r="L358" t="n">
-        <v>1897.144765468527</v>
+        <v>2304.696074558392</v>
       </c>
       <c r="M358" t="n">
-        <v>2194.770566540544</v>
+        <v>2148.852877740213</v>
       </c>
       <c r="N358" t="n">
         <v>65.378</v>
@@ -43043,10 +43043,10 @@
         <v>0</v>
       </c>
       <c r="Q358" t="n">
-        <v>1.079236101148701</v>
+        <v>0.9528186602296449</v>
       </c>
       <c r="R358" t="n">
-        <v>150.3223545314725</v>
+        <v>-101.3857577402136</v>
       </c>
       <c r="S358" t="n">
         <v>0</v>
@@ -43147,10 +43147,10 @@
         <v>26.6</v>
       </c>
       <c r="L359" t="n">
-        <v>2059.913076100859</v>
+        <v>2250.162292079889</v>
       </c>
       <c r="M359" t="n">
-        <v>2338.48951730038</v>
+        <v>2125.258762776653</v>
       </c>
       <c r="N359" t="n">
         <v>64.702</v>
@@ -43162,13 +43162,13 @@
         <v>0</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.9875323884294868</v>
+        <v>0.9571685648957485</v>
       </c>
       <c r="R359" t="n">
-        <v>-25.68219610085907</v>
+        <v>-91.02788277665286</v>
       </c>
       <c r="S359" t="n">
-        <v>0.08753238842948674</v>
+        <v>0.05716856489574851</v>
       </c>
       <c r="T359" t="n">
         <v>0.9914454612489136</v>
@@ -43266,10 +43266,10 @@
         <v>26.6</v>
       </c>
       <c r="L360" t="n">
-        <v>2047.950198703286</v>
+        <v>2248.525814323983</v>
       </c>
       <c r="M360" t="n">
-        <v>2221.583333460699</v>
+        <v>2134.989527737568</v>
       </c>
       <c r="N360" t="n">
         <v>67.26499999999999</v>
@@ -43281,13 +43281,13 @@
         <v>0</v>
       </c>
       <c r="Q360" t="n">
-        <v>1.032647962503198</v>
+        <v>0.9905489336240719</v>
       </c>
       <c r="R360" t="n">
-        <v>66.86140129671389</v>
+        <v>-20.17792773756855</v>
       </c>
       <c r="S360" t="n">
-        <v>0.1326479625031977</v>
+        <v>0.0905489336240719</v>
       </c>
       <c r="T360" t="n">
         <v>1.019254799485697</v>
@@ -43302,7 +43302,7 @@
         <v>0.2253165487596696</v>
       </c>
       <c r="X360" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y360" t="n">
         <v>2</v>
@@ -43385,10 +43385,10 @@
         <v>26.6</v>
       </c>
       <c r="L361" t="n">
-        <v>2263.730666801088</v>
+        <v>2142.676132958674</v>
       </c>
       <c r="M361" t="n">
-        <v>2629.244018708134</v>
+        <v>2258.121287060907</v>
       </c>
       <c r="N361" t="n">
         <v>68.613</v>
@@ -43400,13 +43400,13 @@
         <v>44.41118000000006</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.9529370042273664</v>
+        <v>1.006774979576719</v>
       </c>
       <c r="R361" t="n">
-        <v>-106.5379468010879</v>
+        <v>14.51658704132569</v>
       </c>
       <c r="S361" t="n">
-        <v>0.05293700422736636</v>
+        <v>0.1067749795767193</v>
       </c>
       <c r="T361" t="n">
         <v>1.029142873202775</v>
@@ -43421,7 +43421,7 @@
         <v>0.2245723306997642</v>
       </c>
       <c r="X361" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y361" t="n">
         <v>3</v>
@@ -43504,10 +43504,10 @@
         <v>26.6</v>
       </c>
       <c r="L362" t="n">
-        <v>2433.618373589949</v>
+        <v>2166.695310561647</v>
       </c>
       <c r="M362" t="n">
-        <v>2266.389181079187</v>
+        <v>2570.670395582412</v>
       </c>
       <c r="N362" t="n">
         <v>68.508</v>
@@ -43519,13 +43519,13 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q362" t="n">
-        <v>0.9503626023194438</v>
+        <v>0.9940906363251778</v>
       </c>
       <c r="R362" t="n">
-        <v>-112.4976610791873</v>
+        <v>-12.80379056164657</v>
       </c>
       <c r="S362" t="n">
-        <v>0.05036260231944378</v>
+        <v>0.09409063632517778</v>
       </c>
       <c r="T362" t="n">
         <v>1.015267388620419</v>
@@ -43623,10 +43623,10 @@
         <v>26.6</v>
       </c>
       <c r="L363" t="n">
-        <v>2433.618373589949</v>
+        <v>2166.695310561647</v>
       </c>
       <c r="M363" t="n">
-        <v>2266.389181079187</v>
+        <v>2570.670395582412</v>
       </c>
       <c r="N363" t="n">
         <v>68.02199999999999</v>
@@ -43638,10 +43638,10 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q363" t="n">
-        <v>0.9503626023194438</v>
+        <v>0.9940906363251778</v>
       </c>
       <c r="R363" t="n">
-        <v>-112.4976610791873</v>
+        <v>-12.80379056164657</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -43742,10 +43742,10 @@
         <v>26.6</v>
       </c>
       <c r="L364" t="n">
-        <v>2433.618373589949</v>
+        <v>2166.695310561647</v>
       </c>
       <c r="M364" t="n">
-        <v>2266.389181079187</v>
+        <v>2570.670395582412</v>
       </c>
       <c r="N364" t="n">
         <v>68.02199999999999</v>
@@ -43757,10 +43757,10 @@
         <v>100.0611466666664</v>
       </c>
       <c r="Q364" t="n">
-        <v>0.9503626023194438</v>
+        <v>0.9940906363251778</v>
       </c>
       <c r="R364" t="n">
-        <v>-112.4976610791873</v>
+        <v>-12.80379056164657</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -43861,10 +43861,10 @@
         <v>26.6</v>
       </c>
       <c r="L365" t="n">
-        <v>2433.618373589949</v>
+        <v>2166.695310561647</v>
       </c>
       <c r="M365" t="n">
-        <v>2266.389181079187</v>
+        <v>2570.670395582412</v>
       </c>
       <c r="N365" t="n">
         <v>68.02199999999999</v>
@@ -43876,10 +43876,10 @@
         <v>95.41112000000021</v>
       </c>
       <c r="Q365" t="n">
-        <v>0.9503626023194438</v>
+        <v>0.9940906363251778</v>
       </c>
       <c r="R365" t="n">
-        <v>-112.4976610791873</v>
+        <v>-12.80379056164657</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -43980,10 +43980,10 @@
         <v>26.6</v>
       </c>
       <c r="L366" t="n">
-        <v>2433.618373589949</v>
+        <v>2166.695310561647</v>
       </c>
       <c r="M366" t="n">
-        <v>2266.389181079187</v>
+        <v>2570.670395582412</v>
       </c>
       <c r="N366" t="n">
         <v>68.02199999999999</v>
@@ -43995,10 +43995,10 @@
         <v>65.46594000000005</v>
       </c>
       <c r="Q366" t="n">
-        <v>0.9503626023194438</v>
+        <v>0.9940906363251778</v>
       </c>
       <c r="R366" t="n">
-        <v>-112.4976610791873</v>
+        <v>-12.80379056164657</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>

--- a/data/features_realtime.xlsx
+++ b/data/features_realtime.xlsx
@@ -42790,10 +42790,10 @@
         <v>26.6</v>
       </c>
       <c r="L356" t="n">
-        <v>2306.521189409711</v>
+        <v>2121.486031926037</v>
       </c>
       <c r="M356" t="n">
-        <v>2206.743157840859</v>
+        <v>2204.277869446338</v>
       </c>
       <c r="N356" t="n">
         <v>65.096</v>
@@ -42805,13 +42805,13 @@
         <v>0</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.9262584060752209</v>
+        <v>0.9634823747311376</v>
       </c>
       <c r="R356" t="n">
-        <v>-162.7287578408591</v>
+        <v>-77.47163192603739</v>
       </c>
       <c r="S356" t="n">
-        <v>0.0262584060752209</v>
+        <v>0.0634823747311376</v>
       </c>
       <c r="T356" t="n">
         <v>0</v>
@@ -42826,7 +42826,7 @@
         <v>0.2275213714227406</v>
       </c>
       <c r="X356" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y356" t="n">
         <v>3</v>
@@ -42909,10 +42909,10 @@
         <v>26.6</v>
       </c>
       <c r="L357" t="n">
-        <v>2304.696074558392</v>
+        <v>2137.451058548385</v>
       </c>
       <c r="M357" t="n">
-        <v>2148.852877740213</v>
+        <v>2199.661963964817</v>
       </c>
       <c r="N357" t="n">
         <v>65.12299999999999</v>
@@ -42924,13 +42924,13 @@
         <v>0</v>
       </c>
       <c r="Q357" t="n">
-        <v>0.9528186602296449</v>
+        <v>0.9579012870542848</v>
       </c>
       <c r="R357" t="n">
-        <v>-101.3857577402136</v>
+        <v>-89.98393854838559</v>
       </c>
       <c r="S357" t="n">
-        <v>0.05281866022964488</v>
+        <v>0.05790128705428477</v>
       </c>
       <c r="T357" t="n">
         <v>0</v>
@@ -43028,10 +43028,10 @@
         <v>26.6</v>
       </c>
       <c r="L358" t="n">
-        <v>2304.696074558392</v>
+        <v>2137.451058548385</v>
       </c>
       <c r="M358" t="n">
-        <v>2148.852877740213</v>
+        <v>2199.661963964817</v>
       </c>
       <c r="N358" t="n">
         <v>65.378</v>
@@ -43043,10 +43043,10 @@
         <v>0</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.9528186602296449</v>
+        <v>0.9579012870542848</v>
       </c>
       <c r="R358" t="n">
-        <v>-101.3857577402136</v>
+        <v>-89.98393854838559</v>
       </c>
       <c r="S358" t="n">
         <v>0</v>
@@ -43147,10 +43147,10 @@
         <v>26.6</v>
       </c>
       <c r="L359" t="n">
-        <v>2250.162292079889</v>
+        <v>2106.504763743534</v>
       </c>
       <c r="M359" t="n">
-        <v>2125.258762776653</v>
+        <v>2348.108143092778</v>
       </c>
       <c r="N359" t="n">
         <v>64.702</v>
@@ -43162,13 +43162,13 @@
         <v>0</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.9571685648957485</v>
+        <v>0.9656901398997743</v>
       </c>
       <c r="R359" t="n">
-        <v>-91.02788277665286</v>
+        <v>-72.27388374353404</v>
       </c>
       <c r="S359" t="n">
-        <v>0.05716856489574851</v>
+        <v>0.06569013989977424</v>
       </c>
       <c r="T359" t="n">
         <v>0.9914454612489136</v>
@@ -43266,10 +43266,10 @@
         <v>26.6</v>
       </c>
       <c r="L360" t="n">
-        <v>2248.525814323983</v>
+        <v>2006.221010773496</v>
       </c>
       <c r="M360" t="n">
-        <v>2134.989527737568</v>
+        <v>2470.765597478546</v>
       </c>
       <c r="N360" t="n">
         <v>67.26499999999999</v>
@@ -43281,13 +43281,13 @@
         <v>0</v>
       </c>
       <c r="Q360" t="n">
-        <v>0.9905489336240719</v>
+        <v>1.054126932497623</v>
       </c>
       <c r="R360" t="n">
-        <v>-20.17792773756855</v>
+        <v>108.5905892265037</v>
       </c>
       <c r="S360" t="n">
-        <v>0.0905489336240719</v>
+        <v>0.1541269324976228</v>
       </c>
       <c r="T360" t="n">
         <v>1.019254799485697</v>
@@ -43302,7 +43302,7 @@
         <v>0.2253165487596696</v>
       </c>
       <c r="X360" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y360" t="n">
         <v>2</v>
@@ -43385,10 +43385,10 @@
         <v>26.6</v>
       </c>
       <c r="L361" t="n">
-        <v>2142.676132958674</v>
+        <v>2128.121264238786</v>
       </c>
       <c r="M361" t="n">
-        <v>2258.121287060907</v>
+        <v>2377.311103093575</v>
       </c>
       <c r="N361" t="n">
         <v>68.613</v>
@@ -43400,13 +43400,13 @@
         <v>44.41118000000006</v>
       </c>
       <c r="Q361" t="n">
-        <v>1.006774979576719</v>
+        <v>1.013660619932107</v>
       </c>
       <c r="R361" t="n">
-        <v>14.51658704132569</v>
+        <v>29.07145576121411</v>
       </c>
       <c r="S361" t="n">
-        <v>0.1067749795767193</v>
+        <v>0.1136606199321067</v>
       </c>
       <c r="T361" t="n">
         <v>1.029142873202775</v>
@@ -43504,10 +43504,10 @@
         <v>26.6</v>
       </c>
       <c r="L362" t="n">
-        <v>2166.695310561647</v>
+        <v>2054.551017204182</v>
       </c>
       <c r="M362" t="n">
-        <v>2570.670395582412</v>
+        <v>2458.971937861751</v>
       </c>
       <c r="N362" t="n">
         <v>68.508</v>
@@ -43519,13 +43519,13 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q362" t="n">
-        <v>0.9940906363251778</v>
+        <v>1.048351441245763</v>
       </c>
       <c r="R362" t="n">
-        <v>-12.80379056164657</v>
+        <v>99.34050279581834</v>
       </c>
       <c r="S362" t="n">
-        <v>0.09409063632517778</v>
+        <v>0.1483514412457626</v>
       </c>
       <c r="T362" t="n">
         <v>1.015267388620419</v>
@@ -43540,7 +43540,7 @@
         <v>0.2245949852590114</v>
       </c>
       <c r="X362" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y362" t="n">
         <v>4</v>
@@ -43623,10 +43623,10 @@
         <v>26.6</v>
       </c>
       <c r="L363" t="n">
-        <v>2166.695310561647</v>
+        <v>2054.551017204182</v>
       </c>
       <c r="M363" t="n">
-        <v>2570.670395582412</v>
+        <v>2458.971937861751</v>
       </c>
       <c r="N363" t="n">
         <v>68.02199999999999</v>
@@ -43638,10 +43638,10 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q363" t="n">
-        <v>0.9940906363251778</v>
+        <v>1.048351441245763</v>
       </c>
       <c r="R363" t="n">
-        <v>-12.80379056164657</v>
+        <v>99.34050279581834</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -43742,10 +43742,10 @@
         <v>26.6</v>
       </c>
       <c r="L364" t="n">
-        <v>2166.695310561647</v>
+        <v>2054.551017204182</v>
       </c>
       <c r="M364" t="n">
-        <v>2570.670395582412</v>
+        <v>2458.971937861751</v>
       </c>
       <c r="N364" t="n">
         <v>68.02199999999999</v>
@@ -43757,10 +43757,10 @@
         <v>100.0611466666664</v>
       </c>
       <c r="Q364" t="n">
-        <v>0.9940906363251778</v>
+        <v>1.048351441245763</v>
       </c>
       <c r="R364" t="n">
-        <v>-12.80379056164657</v>
+        <v>99.34050279581834</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -43861,10 +43861,10 @@
         <v>26.6</v>
       </c>
       <c r="L365" t="n">
-        <v>2166.695310561647</v>
+        <v>2054.551017204182</v>
       </c>
       <c r="M365" t="n">
-        <v>2570.670395582412</v>
+        <v>2458.971937861751</v>
       </c>
       <c r="N365" t="n">
         <v>68.02199999999999</v>
@@ -43876,10 +43876,10 @@
         <v>95.41112000000021</v>
       </c>
       <c r="Q365" t="n">
-        <v>0.9940906363251778</v>
+        <v>1.048351441245763</v>
       </c>
       <c r="R365" t="n">
-        <v>-12.80379056164657</v>
+        <v>99.34050279581834</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -43980,10 +43980,10 @@
         <v>26.6</v>
       </c>
       <c r="L366" t="n">
-        <v>2166.695310561647</v>
+        <v>2054.551017204182</v>
       </c>
       <c r="M366" t="n">
-        <v>2570.670395582412</v>
+        <v>2458.971937861751</v>
       </c>
       <c r="N366" t="n">
         <v>68.02199999999999</v>
@@ -43995,10 +43995,10 @@
         <v>65.46594000000005</v>
       </c>
       <c r="Q366" t="n">
-        <v>0.9940906363251778</v>
+        <v>1.048351441245763</v>
       </c>
       <c r="R366" t="n">
-        <v>-12.80379056164657</v>
+        <v>99.34050279581834</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>

--- a/data/features_realtime.xlsx
+++ b/data/features_realtime.xlsx
@@ -42790,10 +42790,10 @@
         <v>26.6</v>
       </c>
       <c r="L356" t="n">
-        <v>2121.486031926037</v>
+        <v>2318.213991178024</v>
       </c>
       <c r="M356" t="n">
-        <v>2204.277869446338</v>
+        <v>2339.449039318305</v>
       </c>
       <c r="N356" t="n">
         <v>65.096</v>
@@ -42805,13 +42805,13 @@
         <v>0</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.9634823747311376</v>
+        <v>0.8817194649750308</v>
       </c>
       <c r="R356" t="n">
-        <v>-77.47163192603739</v>
+        <v>-274.1995911780241</v>
       </c>
       <c r="S356" t="n">
-        <v>0.0634823747311376</v>
+        <v>0</v>
       </c>
       <c r="T356" t="n">
         <v>0</v>
@@ -42826,7 +42826,7 @@
         <v>0.2275213714227406</v>
       </c>
       <c r="X356" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y356" t="n">
         <v>3</v>
@@ -42909,10 +42909,10 @@
         <v>26.6</v>
       </c>
       <c r="L357" t="n">
-        <v>2137.451058548385</v>
+        <v>2134.737528447982</v>
       </c>
       <c r="M357" t="n">
-        <v>2199.661963964817</v>
+        <v>2092.112057484215</v>
       </c>
       <c r="N357" t="n">
         <v>65.12299999999999</v>
@@ -42924,13 +42924,13 @@
         <v>0</v>
       </c>
       <c r="Q357" t="n">
-        <v>0.9579012870542848</v>
+        <v>0.9786603507563167</v>
       </c>
       <c r="R357" t="n">
-        <v>-89.98393854838559</v>
+        <v>-44.64493748421501</v>
       </c>
       <c r="S357" t="n">
-        <v>0.05790128705428477</v>
+        <v>0.07866035075631672</v>
       </c>
       <c r="T357" t="n">
         <v>0</v>
@@ -43028,10 +43028,10 @@
         <v>26.6</v>
       </c>
       <c r="L358" t="n">
-        <v>2137.451058548385</v>
+        <v>2134.737528447982</v>
       </c>
       <c r="M358" t="n">
-        <v>2199.661963964817</v>
+        <v>2092.112057484215</v>
       </c>
       <c r="N358" t="n">
         <v>65.378</v>
@@ -43043,10 +43043,10 @@
         <v>0</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.9579012870542848</v>
+        <v>0.9786603507563167</v>
       </c>
       <c r="R358" t="n">
-        <v>-89.98393854838559</v>
+        <v>-44.64493748421501</v>
       </c>
       <c r="S358" t="n">
         <v>0</v>
@@ -43147,10 +43147,10 @@
         <v>26.6</v>
       </c>
       <c r="L359" t="n">
-        <v>2106.504763743534</v>
+        <v>2140.667242251974</v>
       </c>
       <c r="M359" t="n">
-        <v>2348.108143092778</v>
+        <v>2239.697690094171</v>
       </c>
       <c r="N359" t="n">
         <v>64.702</v>
@@ -43162,13 +43162,13 @@
         <v>0</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.9656901398997743</v>
+        <v>0.9502788849419898</v>
       </c>
       <c r="R359" t="n">
-        <v>-72.27388374353404</v>
+        <v>-106.4363622519736</v>
       </c>
       <c r="S359" t="n">
-        <v>0.06569013989977424</v>
+        <v>0.05027888494198973</v>
       </c>
       <c r="T359" t="n">
         <v>0.9914454612489136</v>
@@ -43266,10 +43266,10 @@
         <v>26.6</v>
       </c>
       <c r="L360" t="n">
-        <v>2006.221010773496</v>
+        <v>2107.481948443134</v>
       </c>
       <c r="M360" t="n">
-        <v>2470.765597478546</v>
+        <v>2238.171496253942</v>
       </c>
       <c r="N360" t="n">
         <v>67.26499999999999</v>
@@ -43281,13 +43281,13 @@
         <v>0</v>
       </c>
       <c r="Q360" t="n">
-        <v>1.054126932497623</v>
+        <v>1.003477919021454</v>
       </c>
       <c r="R360" t="n">
-        <v>108.5905892265037</v>
+        <v>7.329651556865883</v>
       </c>
       <c r="S360" t="n">
-        <v>0.1541269324976228</v>
+        <v>0.1034779190214544</v>
       </c>
       <c r="T360" t="n">
         <v>1.019254799485697</v>
@@ -43385,10 +43385,10 @@
         <v>26.6</v>
       </c>
       <c r="L361" t="n">
-        <v>2128.121264238786</v>
+        <v>2446.801255439505</v>
       </c>
       <c r="M361" t="n">
-        <v>2377.311103093575</v>
+        <v>2192.781026457506</v>
       </c>
       <c r="N361" t="n">
         <v>68.613</v>
@@ -43400,13 +43400,13 @@
         <v>44.41118000000006</v>
       </c>
       <c r="Q361" t="n">
-        <v>1.013660619932107</v>
+        <v>0.9837702415202016</v>
       </c>
       <c r="R361" t="n">
-        <v>29.07145576121411</v>
+        <v>-35.58830645750595</v>
       </c>
       <c r="S361" t="n">
-        <v>0.1136606199321067</v>
+        <v>0.08377024152020163</v>
       </c>
       <c r="T361" t="n">
         <v>1.029142873202775</v>
@@ -43421,7 +43421,7 @@
         <v>0.2245723306997642</v>
       </c>
       <c r="X361" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y361" t="n">
         <v>3</v>
@@ -43504,10 +43504,10 @@
         <v>26.6</v>
       </c>
       <c r="L362" t="n">
-        <v>2054.551017204182</v>
+        <v>2186.083020786982</v>
       </c>
       <c r="M362" t="n">
-        <v>2458.971937861751</v>
+        <v>2486.453405781319</v>
       </c>
       <c r="N362" t="n">
         <v>68.508</v>
@@ -43519,13 +43519,13 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q362" t="n">
-        <v>1.048351441245763</v>
+        <v>0.9852743466364885</v>
       </c>
       <c r="R362" t="n">
-        <v>99.34050279581834</v>
+        <v>-32.19150078698203</v>
       </c>
       <c r="S362" t="n">
-        <v>0.1483514412457626</v>
+        <v>0.08527434663648847</v>
       </c>
       <c r="T362" t="n">
         <v>1.015267388620419</v>
@@ -43540,7 +43540,7 @@
         <v>0.2245949852590114</v>
       </c>
       <c r="X362" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y362" t="n">
         <v>4</v>
@@ -43623,10 +43623,10 @@
         <v>26.6</v>
       </c>
       <c r="L363" t="n">
-        <v>2054.551017204182</v>
+        <v>2186.083020786982</v>
       </c>
       <c r="M363" t="n">
-        <v>2458.971937861751</v>
+        <v>2486.453405781319</v>
       </c>
       <c r="N363" t="n">
         <v>68.02199999999999</v>
@@ -43638,10 +43638,10 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q363" t="n">
-        <v>1.048351441245763</v>
+        <v>0.9852743466364885</v>
       </c>
       <c r="R363" t="n">
-        <v>99.34050279581834</v>
+        <v>-32.19150078698203</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -43742,10 +43742,10 @@
         <v>26.6</v>
       </c>
       <c r="L364" t="n">
-        <v>2054.551017204182</v>
+        <v>2186.083020786982</v>
       </c>
       <c r="M364" t="n">
-        <v>2458.971937861751</v>
+        <v>2486.453405781319</v>
       </c>
       <c r="N364" t="n">
         <v>68.02199999999999</v>
@@ -43757,10 +43757,10 @@
         <v>100.0611466666664</v>
       </c>
       <c r="Q364" t="n">
-        <v>1.048351441245763</v>
+        <v>0.9852743466364885</v>
       </c>
       <c r="R364" t="n">
-        <v>99.34050279581834</v>
+        <v>-32.19150078698203</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -43861,10 +43861,10 @@
         <v>26.6</v>
       </c>
       <c r="L365" t="n">
-        <v>2054.551017204182</v>
+        <v>2186.083020786982</v>
       </c>
       <c r="M365" t="n">
-        <v>2458.971937861751</v>
+        <v>2486.453405781319</v>
       </c>
       <c r="N365" t="n">
         <v>68.02199999999999</v>
@@ -43876,10 +43876,10 @@
         <v>95.41112000000021</v>
       </c>
       <c r="Q365" t="n">
-        <v>1.048351441245763</v>
+        <v>0.9852743466364885</v>
       </c>
       <c r="R365" t="n">
-        <v>99.34050279581834</v>
+        <v>-32.19150078698203</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -43980,10 +43980,10 @@
         <v>26.6</v>
       </c>
       <c r="L366" t="n">
-        <v>2054.551017204182</v>
+        <v>2186.083020786982</v>
       </c>
       <c r="M366" t="n">
-        <v>2458.971937861751</v>
+        <v>2486.453405781319</v>
       </c>
       <c r="N366" t="n">
         <v>68.02199999999999</v>
@@ -43995,10 +43995,10 @@
         <v>65.46594000000005</v>
       </c>
       <c r="Q366" t="n">
-        <v>1.048351441245763</v>
+        <v>0.9852743466364885</v>
       </c>
       <c r="R366" t="n">
-        <v>99.34050279581834</v>
+        <v>-32.19150078698203</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>

--- a/data/features_realtime.xlsx
+++ b/data/features_realtime.xlsx
@@ -42195,10 +42195,10 @@
         <v>26.6</v>
       </c>
       <c r="L351" t="n">
-        <v>2137.336765775275</v>
+        <v>2154.865874721704</v>
       </c>
       <c r="M351" t="n">
-        <v>2299.626502367492</v>
+        <v>2196.236590741705</v>
       </c>
       <c r="N351" t="n">
         <v>65.096</v>
@@ -42210,13 +42210,13 @@
         <v>0</v>
       </c>
       <c r="Q351" t="n">
-        <v>0.9563370792705285</v>
+        <v>0.9485575988635632</v>
       </c>
       <c r="R351" t="n">
-        <v>-93.32236577527465</v>
+        <v>-110.8514747217041</v>
       </c>
       <c r="S351" t="n">
-        <v>0.05633707927052845</v>
+        <v>0.04855759886356315</v>
       </c>
       <c r="T351" t="n">
         <v>0</v>
@@ -42231,7 +42231,7 @@
         <v>0.2275213714227406</v>
       </c>
       <c r="X351" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y351" t="n">
         <v>3</v>
@@ -42314,10 +42314,10 @@
         <v>26.6</v>
       </c>
       <c r="L352" t="n">
-        <v>2142.7297732719</v>
+        <v>2195.763532908104</v>
       </c>
       <c r="M352" t="n">
-        <v>2261.254448120066</v>
+        <v>2270.050639279503</v>
       </c>
       <c r="N352" t="n">
         <v>65.12299999999999</v>
@@ -42329,13 +42329,13 @@
         <v>0</v>
       </c>
       <c r="Q352" t="n">
-        <v>0.9555414525615185</v>
+        <v>0.9324624848320389</v>
       </c>
       <c r="R352" t="n">
-        <v>-95.26265327190004</v>
+        <v>-148.2964129081047</v>
       </c>
       <c r="S352" t="n">
-        <v>0.05554145256151843</v>
+        <v>0.03246248483203884</v>
       </c>
       <c r="T352" t="n">
         <v>0</v>
@@ -42350,7 +42350,7 @@
         <v>0.2275890184142461</v>
       </c>
       <c r="X352" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y352" t="n">
         <v>4</v>
@@ -42433,10 +42433,10 @@
         <v>26.6</v>
       </c>
       <c r="L353" t="n">
-        <v>2142.7297732719</v>
+        <v>2195.763532908104</v>
       </c>
       <c r="M353" t="n">
-        <v>2261.254448120066</v>
+        <v>2270.050639279503</v>
       </c>
       <c r="N353" t="n">
         <v>65.378</v>
@@ -42448,10 +42448,10 @@
         <v>0</v>
       </c>
       <c r="Q353" t="n">
-        <v>0.9555414525615185</v>
+        <v>0.9324624848320389</v>
       </c>
       <c r="R353" t="n">
-        <v>-95.26265327190004</v>
+        <v>-148.2964129081047</v>
       </c>
       <c r="S353" t="n">
         <v>0</v>
@@ -42552,10 +42552,10 @@
         <v>26.6</v>
       </c>
       <c r="L354" t="n">
-        <v>1966.38467364345</v>
+        <v>2213.449719986828</v>
       </c>
       <c r="M354" t="n">
-        <v>2136.284756529085</v>
+        <v>2171.769316088571</v>
       </c>
       <c r="N354" t="n">
         <v>64.702</v>
@@ -42567,13 +42567,13 @@
         <v>0</v>
       </c>
       <c r="Q354" t="n">
-        <v>1.034503018287772</v>
+        <v>0.9366698686317113</v>
       </c>
       <c r="R354" t="n">
-        <v>67.8462063565496</v>
+        <v>-137.538436088571</v>
       </c>
       <c r="S354" t="n">
-        <v>0.1345030182877723</v>
+        <v>0.03666986863171129</v>
       </c>
       <c r="T354" t="n">
         <v>0.9914454612489136</v>
@@ -42588,7 +42588,7 @@
         <v>0.2264938559987557</v>
       </c>
       <c r="X354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y354" t="n">
         <v>1</v>
@@ -42671,10 +42671,10 @@
         <v>26.6</v>
       </c>
       <c r="L355" t="n">
-        <v>2206.972654906721</v>
+        <v>2308.323742121202</v>
       </c>
       <c r="M355" t="n">
-        <v>2454.449231780323</v>
+        <v>2277.564569531345</v>
       </c>
       <c r="N355" t="n">
         <v>67.26499999999999</v>
@@ -42686,13 +42686,13 @@
         <v>0</v>
       </c>
       <c r="Q355" t="n">
-        <v>0.9582409620242552</v>
+        <v>0.9285407879497514</v>
       </c>
       <c r="R355" t="n">
-        <v>-92.1610549067218</v>
+        <v>-162.7529695313451</v>
       </c>
       <c r="S355" t="n">
-        <v>0.05824096202425522</v>
+        <v>0.02854078794975135</v>
       </c>
       <c r="T355" t="n">
         <v>1.019254799485697</v>
@@ -42707,7 +42707,7 @@
         <v>0.2253165487596696</v>
       </c>
       <c r="X355" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y355" t="n">
         <v>2</v>
@@ -42790,10 +42790,10 @@
         <v>26.6</v>
       </c>
       <c r="L356" t="n">
-        <v>2419.491837488018</v>
+        <v>2167.263121301295</v>
       </c>
       <c r="M356" t="n">
-        <v>2346.33842857807</v>
+        <v>2180.999487705672</v>
       </c>
       <c r="N356" t="n">
         <v>68.613</v>
@@ -42805,13 +42805,13 @@
         <v>44.41118000000006</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.9193868598514086</v>
+        <v>0.9953534016228526</v>
       </c>
       <c r="R356" t="n">
-        <v>-189.1457085780703</v>
+        <v>-10.07040130129462</v>
       </c>
       <c r="S356" t="n">
-        <v>0.01938685985140853</v>
+        <v>0.09535340162285255</v>
       </c>
       <c r="T356" t="n">
         <v>1.029142873202775</v>
@@ -42826,7 +42826,7 @@
         <v>0.2245723306997642</v>
       </c>
       <c r="X356" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y356" t="n">
         <v>3</v>
@@ -42909,10 +42909,10 @@
         <v>26.6</v>
       </c>
       <c r="L357" t="n">
-        <v>2248.797267207065</v>
+        <v>2266.081142510981</v>
       </c>
       <c r="M357" t="n">
-        <v>2257.342063306739</v>
+        <v>2299.078261335058</v>
       </c>
       <c r="N357" t="n">
         <v>68.508</v>
@@ -42924,13 +42924,13 @@
         <v>69.29092000000014</v>
       </c>
       <c r="Q357" t="n">
-        <v>0.9577971084401519</v>
+        <v>0.9504917893683114</v>
       </c>
       <c r="R357" t="n">
-        <v>-94.90574720706491</v>
+        <v>-112.1896225109808</v>
       </c>
       <c r="S357" t="n">
-        <v>0.05779710844015185</v>
+        <v>0.05049178936831134</v>
       </c>
       <c r="T357" t="n">
         <v>1.015267388620419</v>
@@ -43028,10 +43028,10 @@
         <v>26.6</v>
       </c>
       <c r="L358" t="n">
-        <v>2353.07829813434</v>
+        <v>2295.468277316978</v>
       </c>
       <c r="M358" t="n">
-        <v>2436.082674974659</v>
+        <v>2472.308156056114</v>
       </c>
       <c r="N358" t="n">
         <v>68.02199999999999</v>
@@ -43043,13 +43043,13 @@
         <v>73.87087600000018</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.908567922152939</v>
+        <v>0.9313705099414206</v>
       </c>
       <c r="R358" t="n">
-        <v>-215.1468381343402</v>
+        <v>-157.5368173169786</v>
       </c>
       <c r="S358" t="n">
-        <v>0.008567922152939</v>
+        <v>0.03137050994142054</v>
       </c>
       <c r="T358" t="n">
         <v>1.000361744149479</v>
@@ -43147,10 +43147,10 @@
         <v>26.6</v>
       </c>
       <c r="L359" t="n">
-        <v>2281.951534906334</v>
+        <v>2116.65306731546</v>
       </c>
       <c r="M359" t="n">
-        <v>2395.428289708972</v>
+        <v>2324.216216630054</v>
       </c>
       <c r="N359" t="n">
         <v>67.297</v>
@@ -43162,13 +43162,13 @@
         <v>94.1594566666663</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.9274914991066832</v>
+        <v>0.9999232669165447</v>
       </c>
       <c r="R359" t="n">
-        <v>-165.4608849063343</v>
+        <v>-0.162417315460516</v>
       </c>
       <c r="S359" t="n">
-        <v>0.02749149910668314</v>
+        <v>0.09992326691654463</v>
       </c>
       <c r="T359" t="n">
         <v>0.9868074609768739</v>
@@ -43183,7 +43183,7 @@
         <v>0.2238763675534403</v>
       </c>
       <c r="X359" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y359" t="n">
         <v>1</v>
@@ -43266,10 +43266,10 @@
         <v>26.6</v>
       </c>
       <c r="L360" t="n">
-        <v>2276.691267476561</v>
+        <v>2301.445109856568</v>
       </c>
       <c r="M360" t="n">
-        <v>2192.735535825738</v>
+        <v>2308.740647391519</v>
       </c>
       <c r="N360" t="n">
         <v>66.91699999999999</v>
@@ -43281,13 +43281,13 @@
         <v>72.00452399999995</v>
       </c>
       <c r="Q360" t="n">
-        <v>0.9555056849161003</v>
+        <v>0.9103720358247717</v>
       </c>
       <c r="R360" t="n">
-        <v>-97.5642658257384</v>
+        <v>-206.2738398565684</v>
       </c>
       <c r="S360" t="n">
-        <v>0.05550568491610031</v>
+        <v>0.01037203582477164</v>
       </c>
       <c r="T360" t="n">
         <v>0.9825697764791702</v>
@@ -43302,7 +43302,7 @@
         <v>0.2222591866547112</v>
       </c>
       <c r="X360" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y360" t="n">
         <v>2</v>
@@ -43385,10 +43385,10 @@
         <v>26.6</v>
       </c>
       <c r="L361" t="n">
-        <v>2205.876950258823</v>
+        <v>2213.514790208246</v>
       </c>
       <c r="M361" t="n">
-        <v>2421.450667166237</v>
+        <v>2323.466024524218</v>
       </c>
       <c r="N361" t="n">
         <v>67.06799999999998</v>
@@ -43400,13 +43400,13 @@
         <v>31.84880799999974</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.9510444541128626</v>
+        <v>0.9477628291797787</v>
       </c>
       <c r="R361" t="n">
-        <v>-107.9899102588233</v>
+        <v>-115.6277502082467</v>
       </c>
       <c r="S361" t="n">
-        <v>0.05104445411286263</v>
+        <v>0.0477628291797787</v>
       </c>
       <c r="T361" t="n">
         <v>1.000251249253228</v>
@@ -43421,7 +43421,7 @@
         <v>0.2221693231492478</v>
       </c>
       <c r="X361" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y361" t="n">
         <v>3</v>
@@ -43504,10 +43504,10 @@
         <v>26.6</v>
       </c>
       <c r="L362" t="n">
-        <v>2112.952850584774</v>
+        <v>2236.533037065959</v>
       </c>
       <c r="M362" t="n">
-        <v>2377.381685575695</v>
+        <v>2507.597033753249</v>
       </c>
       <c r="N362" t="n">
         <v>68.26799999999999</v>
@@ -43519,13 +43519,13 @@
         <v>2.504763999999795</v>
       </c>
       <c r="Q362" t="n">
-        <v>1.012896146455266</v>
+        <v>0.9569283192018976</v>
       </c>
       <c r="R362" t="n">
-        <v>27.24894941522598</v>
+        <v>-96.3312370659587</v>
       </c>
       <c r="S362" t="n">
-        <v>0.1128961464552659</v>
+        <v>0.05692831920189756</v>
       </c>
       <c r="T362" t="n">
         <v>0.9994954874012066</v>
@@ -43540,7 +43540,7 @@
         <v>0.2226707020750876</v>
       </c>
       <c r="X362" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y362" t="n">
         <v>4</v>
@@ -43623,10 +43623,10 @@
         <v>27</v>
       </c>
       <c r="L363" t="n">
-        <v>2112.952850584774</v>
+        <v>2236.533037065959</v>
       </c>
       <c r="M363" t="n">
-        <v>2377.381685575695</v>
+        <v>2507.597033753249</v>
       </c>
       <c r="N363" t="n">
         <v>72.96299999999999</v>
@@ -43638,10 +43638,10 @@
         <v>-7.173946000000342</v>
       </c>
       <c r="Q363" t="n">
-        <v>1.012896146455266</v>
+        <v>0.9569283192018976</v>
       </c>
       <c r="R363" t="n">
-        <v>27.24894941522598</v>
+        <v>-96.3312370659587</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -43742,10 +43742,10 @@
         <v>27</v>
       </c>
       <c r="L364" t="n">
-        <v>2112.952850584774</v>
+        <v>2236.533037065959</v>
       </c>
       <c r="M364" t="n">
-        <v>2377.381685575695</v>
+        <v>2507.597033753249</v>
       </c>
       <c r="N364" t="n">
         <v>72.96299999999999</v>
@@ -43757,10 +43757,10 @@
         <v>-24.97688666666681</v>
       </c>
       <c r="Q364" t="n">
-        <v>1.012896146455266</v>
+        <v>0.9569283192018976</v>
       </c>
       <c r="R364" t="n">
-        <v>27.24894941522598</v>
+        <v>-96.3312370659587</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -43861,10 +43861,10 @@
         <v>27</v>
       </c>
       <c r="L365" t="n">
-        <v>2112.952850584774</v>
+        <v>2236.533037065959</v>
       </c>
       <c r="M365" t="n">
-        <v>2377.381685575695</v>
+        <v>2507.597033753249</v>
       </c>
       <c r="N365" t="n">
         <v>72.96299999999999</v>
@@ -43876,10 +43876,10 @@
         <v>-13.09110399999963</v>
       </c>
       <c r="Q365" t="n">
-        <v>1.012896146455266</v>
+        <v>0.9569283192018976</v>
       </c>
       <c r="R365" t="n">
-        <v>27.24894941522598</v>
+        <v>-96.3312370659587</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -43980,10 +43980,10 @@
         <v>27</v>
       </c>
       <c r="L366" t="n">
-        <v>2112.952850584774</v>
+        <v>2236.533037065959</v>
       </c>
       <c r="M366" t="n">
-        <v>2377.381685575695</v>
+        <v>2507.597033753249</v>
       </c>
       <c r="N366" t="n">
         <v>72.96299999999999</v>
@@ -43995,10 +43995,10 @@
         <v>19.927412</v>
       </c>
       <c r="Q366" t="n">
-        <v>1.012896146455266</v>
+        <v>0.9569283192018976</v>
       </c>
       <c r="R366" t="n">
-        <v>27.24894941522598</v>
+        <v>-96.3312370659587</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>
